--- a/Documentação/diario_de_bordo/Diario de Bordo.xlsx
+++ b/Documentação/diario_de_bordo/Diario de Bordo.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>DIARIO DE BORDO - NEXBIT</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Organizando a pasta Data, mudando atributo na tabela funcionário e adicionando PDF do dicionário de dados</t>
+  </si>
+  <si>
+    <t>Atualizando a documentação</t>
   </si>
 </sst>
 </file>
@@ -337,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -426,6 +429,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2390,12 +2396,18 @@
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
       <c r="M86" s="20"/>
-      <c r="N86" s="3"/>
-      <c r="O86" s="3"/>
+      <c r="N86" s="12">
+        <v>45980</v>
+      </c>
+      <c r="O86" s="12">
+        <v>45980</v>
+      </c>
       <c r="P86" s="18"/>
       <c r="Q86" s="20"/>
       <c r="R86" s="20"/>
-      <c r="S86" s="20"/>
+      <c r="S86" s="32" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="87" spans="7:19">
       <c r="G87" s="19">
